--- a/kennzahlen.xlsx
+++ b/kennzahlen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7dae6aef2e77679f/04_RWTH Aachen/93_Masterarbeit/08_KI-Chatbot/Update_KI-Chatbot_08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7dae6aef2e77679f/04_RWTH Aachen/93_Masterarbeit/08_KI-Chatbot/Update_KI-Chatbot_09/chatbot_updates_validierung_v5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_6B5BA27711752E3EE570B0F45350DE38C729AAE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E22EDEB1-E8EE-417E-8F48-A31F4C9B690A}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_6B5BA27711752E3EE570B0F45350DE38C729AAE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52C3A23B-7598-4D9D-BAAD-23DB40BD6D70}"/>
   <bookViews>
-    <workbookView xWindow="34450" yWindow="-4500" windowWidth="46300" windowHeight="25420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kennzahlen" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,11 +201,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -234,12 +229,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -255,10 +247,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -591,7 +579,7 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
@@ -608,7 +596,7 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
@@ -622,7 +610,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="C5" t="s">
@@ -636,7 +624,7 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
@@ -650,7 +638,7 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
@@ -664,7 +652,7 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
@@ -678,7 +666,7 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
@@ -692,7 +680,7 @@
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
@@ -703,16 +691,16 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>18</v>
       </c>
     </row>
@@ -720,7 +708,7 @@
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
@@ -734,7 +722,7 @@
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
@@ -748,7 +736,7 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
@@ -762,7 +750,7 @@
       <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
@@ -776,7 +764,7 @@
       <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" t="s">
@@ -790,7 +778,7 @@
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
